--- a/salidas/empresas/HD.xlsx
+++ b/salidas/empresas/HD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>24.06367492675781</v>
+        <v>24.06368255615234</v>
       </c>
       <c r="C2" t="n">
         <v>40.54999923706055</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>25.0131893157959</v>
+        <v>25.0131778717041</v>
       </c>
       <c r="C3" t="n">
         <v>42.15000152587891</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>25.19259452819824</v>
+        <v>25.19259071350098</v>
       </c>
       <c r="C4" t="n">
         <v>42.29999923706055</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>23.78109359741211</v>
+        <v>23.78109550476074</v>
       </c>
       <c r="C5" t="n">
         <v>39.93000030517578</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>22.70310592651367</v>
+        <v>22.7031192779541</v>
       </c>
       <c r="C6" t="n">
         <v>38.11999893188477</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.40113067626953</v>
+        <v>21.40113258361816</v>
       </c>
       <c r="C7" t="n">
         <v>35.79000091552734</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>20.75533485412598</v>
+        <v>20.75533103942871</v>
       </c>
       <c r="C8" t="n">
         <v>34.70999908447266</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>20.50418472290039</v>
+        <v>20.50418663024902</v>
       </c>
       <c r="C9" t="n">
         <v>34.29000091552734</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>21.7824764251709</v>
+        <v>21.78248023986816</v>
       </c>
       <c r="C10" t="n">
         <v>36.27000045776367</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>22.4190788269043</v>
+        <v>22.41907691955566</v>
       </c>
       <c r="C11" t="n">
         <v>37.33000183105469</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>24.26391220092773</v>
+        <v>24.26391983032227</v>
       </c>
       <c r="C13" t="n">
         <v>40.15999984741211</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>24.61434364318848</v>
+        <v>24.61433601379395</v>
       </c>
       <c r="C14" t="n">
         <v>40.7400016784668</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>23.91952323913574</v>
+        <v>23.91952705383301</v>
       </c>
       <c r="C15" t="n">
         <v>39.59000015258789</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>22.32751846313477</v>
+        <v>22.3275260925293</v>
       </c>
       <c r="C16" t="n">
         <v>36.7400016784668</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>23.01424789428711</v>
+        <v>23.01423835754395</v>
       </c>
       <c r="C17" t="n">
         <v>37.86999893188477</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>23.62196731567383</v>
+        <v>23.62196922302246</v>
       </c>
       <c r="C18" t="n">
         <v>38.86999893188477</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>24.04961776733398</v>
+        <v>24.04963111877441</v>
       </c>
       <c r="C19" t="n">
         <v>39.34999847412109</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>22.7172737121582</v>
+        <v>22.71727561950684</v>
       </c>
       <c r="C20" t="n">
         <v>37.16999816894531</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>23.56441688537598</v>
+        <v>23.56441497802734</v>
       </c>
       <c r="C21" t="n">
         <v>38.31000137329102</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>19.95378494262695</v>
+        <v>19.95378303527832</v>
       </c>
       <c r="C22" t="n">
         <v>32.43999862670898</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>19.38175582885742</v>
+        <v>19.38174438476562</v>
       </c>
       <c r="C23" t="n">
         <v>31.51000022888184</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.71217346191406</v>
+        <v>17.71218109130859</v>
       </c>
       <c r="C24" t="n">
         <v>28.55999946594238</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>16.70749473571777</v>
+        <v>16.7075023651123</v>
       </c>
       <c r="C25" t="n">
         <v>26.94000053405762</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>19.00214195251465</v>
+        <v>19.00214004516602</v>
       </c>
       <c r="C26" t="n">
         <v>30.63999938964844</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>16.46562957763672</v>
+        <v>16.46562576293945</v>
       </c>
       <c r="C27" t="n">
         <v>26.54999923706055</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>17.5038013458252</v>
+        <v>17.50380897521973</v>
       </c>
       <c r="C28" t="n">
         <v>27.96999931335449</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>18.02322959899902</v>
+        <v>18.02323150634766</v>
       </c>
       <c r="C29" t="n">
         <v>28.79999923706055</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.1220760345459</v>
+        <v>17.1220703125</v>
       </c>
       <c r="C30" t="n">
         <v>27.36000061035156</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.7788200378418</v>
+        <v>14.77882099151611</v>
       </c>
       <c r="C31" t="n">
         <v>23.42000007629395</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>15.03753757476807</v>
+        <v>15.0375394821167</v>
       </c>
       <c r="C32" t="n">
         <v>23.82999992370605</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>16.47415733337402</v>
+        <v>16.47415351867676</v>
       </c>
       <c r="C34" t="n">
         <v>25.88999938964844</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.01063919067383</v>
+        <v>15.01063442230225</v>
       </c>
       <c r="C35" t="n">
         <v>23.59000015258789</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>14.70520496368408</v>
+        <v>14.70520687103271</v>
       </c>
       <c r="C36" t="n">
         <v>23.11000061035156</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.80499649047852</v>
+        <v>14.80498504638672</v>
       </c>
       <c r="C37" t="n">
         <v>23.02000045776367</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.84671783447266</v>
+        <v>13.84671497344971</v>
       </c>
       <c r="C38" t="n">
         <v>21.53000068664551</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>13.43511199951172</v>
+        <v>13.4351110458374</v>
       </c>
       <c r="C39" t="n">
         <v>20.88999938964844</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.34163475036621</v>
+        <v>15.34163761138916</v>
       </c>
       <c r="C40" t="n">
         <v>23.55999946594238</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>17.13886833190918</v>
+        <v>17.13886451721191</v>
       </c>
       <c r="C41" t="n">
         <v>26.31999969482422</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.52948760986328</v>
+        <v>15.52947998046875</v>
       </c>
       <c r="C43" t="n">
         <v>23.6299991607666</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>17.04760360717773</v>
+        <v>17.04759979248047</v>
       </c>
       <c r="C44" t="n">
         <v>25.94000053405762</v>
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>17.65317726135254</v>
+        <v>17.65318870544434</v>
       </c>
       <c r="C46" t="n">
         <v>26.63999938964844</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.62606430053711</v>
+        <v>16.62606811523438</v>
       </c>
       <c r="C47" t="n">
         <v>25.09000015258789</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.13030433654785</v>
+        <v>18.13028907775879</v>
       </c>
       <c r="C48" t="n">
         <v>27.36000061035156</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.32963562011719</v>
+        <v>19.32962799072266</v>
       </c>
       <c r="C49" t="n">
         <v>28.93000030517578</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>18.71492195129395</v>
+        <v>18.71492958068848</v>
       </c>
       <c r="C50" t="n">
         <v>28.01000022888184</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>20.84633255004883</v>
+        <v>20.84633636474609</v>
       </c>
       <c r="C51" t="n">
         <v>31.20000076293945</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>21.77549743652344</v>
+        <v>21.77549362182617</v>
       </c>
       <c r="C52" t="n">
         <v>32.34999847412109</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>23.71409225463867</v>
+        <v>23.7141056060791</v>
       </c>
       <c r="C53" t="n">
         <v>35.22999954223633</v>
@@ -1518,11 +1530,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>22.79192161560059</v>
+        <v>22.79191970825195</v>
       </c>
       <c r="C54" t="n">
         <v>33.86000061035156</v>
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>19.02715873718262</v>
+        <v>19.02716064453125</v>
       </c>
       <c r="C55" t="n">
         <v>28.06999969482422</v>
@@ -1568,11 +1580,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>19.32541656494141</v>
+        <v>19.32540130615234</v>
       </c>
       <c r="C56" t="n">
         <v>28.51000022888184</v>
@@ -1593,11 +1605,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>19.01804542541504</v>
+        <v>19.01805305480957</v>
       </c>
       <c r="C57" t="n">
         <v>27.81999969482422</v>
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>21.65678977966309</v>
+        <v>21.65677642822266</v>
       </c>
       <c r="C58" t="n">
         <v>31.68000030517578</v>
@@ -1643,11 +1655,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>21.12355995178223</v>
+        <v>21.12356567382812</v>
       </c>
       <c r="C59" t="n">
         <v>30.89999961853027</v>
@@ -1668,11 +1680,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.81191062927246</v>
+        <v>20.81191444396973</v>
       </c>
       <c r="C60" t="n">
         <v>30.20999908447266</v>
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1718,11 +1730,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.33115196228027</v>
+        <v>25.33114242553711</v>
       </c>
       <c r="C62" t="n">
         <v>36.77000045776367</v>
@@ -1743,11 +1755,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>25.81338691711426</v>
+        <v>25.81339454650879</v>
       </c>
       <c r="C63" t="n">
         <v>37.47000122070312</v>
@@ -1768,11 +1780,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>25.70523643493652</v>
+        <v>25.70523262023926</v>
       </c>
       <c r="C64" t="n">
         <v>37.06000137329102</v>
@@ -1797,11 +1809,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>25.76766014099121</v>
+        <v>25.76765060424805</v>
       </c>
       <c r="C65" t="n">
         <v>37.15000152587891</v>
@@ -1826,11 +1838,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>25.16420745849609</v>
+        <v>25.16421508789062</v>
       </c>
       <c r="C66" t="n">
         <v>36.27999877929688</v>
@@ -1855,11 +1867,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>25.31143379211426</v>
+        <v>25.31142616271973</v>
       </c>
       <c r="C67" t="n">
         <v>36.22000122070312</v>
@@ -1884,11 +1896,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>24.40994453430176</v>
+        <v>24.40994834899902</v>
       </c>
       <c r="C68" t="n">
         <v>34.93000030517578</v>
@@ -1913,7 +1925,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1942,11 +1954,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>23.14056777954102</v>
+        <v>23.14057350158691</v>
       </c>
       <c r="C70" t="n">
         <v>32.86999893188477</v>
@@ -1971,11 +1983,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>25.20330047607422</v>
+        <v>25.20329856872559</v>
       </c>
       <c r="C71" t="n">
         <v>35.79999923706055</v>
@@ -2000,11 +2012,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.82734680175781</v>
+        <v>27.82734489440918</v>
       </c>
       <c r="C72" t="n">
         <v>39.22000122070312</v>
@@ -2029,11 +2041,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>29.82819747924805</v>
+        <v>29.82818984985352</v>
       </c>
       <c r="C73" t="n">
         <v>42.04000091552734</v>
@@ -2058,11 +2070,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>31.49555397033691</v>
+        <v>31.49555206298828</v>
       </c>
       <c r="C74" t="n">
         <v>44.38999938964844</v>
@@ -2087,11 +2099,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>33.75182723999023</v>
+        <v>33.75183868408203</v>
       </c>
       <c r="C75" t="n">
         <v>47.56999969482422</v>
@@ -2116,11 +2128,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>35.91569519042969</v>
+        <v>35.91570281982422</v>
       </c>
       <c r="C76" t="n">
         <v>50.31000137329102</v>
@@ -2145,11 +2157,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>36.97224426269531</v>
+        <v>36.97225952148438</v>
       </c>
       <c r="C77" t="n">
         <v>51.79000091552734</v>
@@ -2174,11 +2186,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>35.43104553222656</v>
+        <v>35.43104934692383</v>
       </c>
       <c r="C78" t="n">
         <v>49.34000015258789</v>
@@ -2203,11 +2215,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>38.05212020874023</v>
+        <v>38.05210494995117</v>
       </c>
       <c r="C79" t="n">
         <v>52.9900016784668</v>
@@ -2232,11 +2244,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>37.47045135498047</v>
+        <v>37.4704475402832</v>
       </c>
       <c r="C80" t="n">
         <v>52.18000030517578</v>
@@ -2261,11 +2273,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>40.96178436279297</v>
+        <v>40.9617919921875</v>
       </c>
       <c r="C81" t="n">
         <v>56.75</v>
@@ -2290,11 +2302,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>43.57467651367188</v>
+        <v>43.57468414306641</v>
       </c>
       <c r="C82" t="n">
         <v>60.36999893188477</v>
@@ -2319,11 +2331,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>44.30369567871094</v>
+        <v>44.30370330810547</v>
       </c>
       <c r="C83" t="n">
         <v>61.38000106811523</v>
@@ -2348,11 +2360,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>47.17866897583008</v>
+        <v>47.17866134643555</v>
       </c>
       <c r="C84" t="n">
         <v>65.06999969482422</v>
@@ -2377,11 +2389,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>44.84402465820312</v>
+        <v>44.84402084350586</v>
       </c>
       <c r="C85" t="n">
         <v>61.84999847412109</v>
@@ -2406,11 +2418,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>48.52000045776367</v>
+        <v>48.52000427246094</v>
       </c>
       <c r="C86" t="n">
         <v>66.91999816894531</v>
@@ -2435,11 +2447,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>49.66556930541992</v>
+        <v>49.66558456420898</v>
       </c>
       <c r="C87" t="n">
         <v>68.5</v>
@@ -2464,11 +2476,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>50.87180328369141</v>
+        <v>50.87182998657227</v>
       </c>
       <c r="C88" t="n">
         <v>69.77999877929688</v>
@@ -2493,11 +2505,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>53.47445297241211</v>
+        <v>53.47444152832031</v>
       </c>
       <c r="C89" t="n">
         <v>73.34999847412109</v>
@@ -2522,11 +2534,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>57.34561157226562</v>
+        <v>57.34562301635742</v>
       </c>
       <c r="C90" t="n">
         <v>78.66000366210938</v>
@@ -2551,11 +2563,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>56.75798416137695</v>
+        <v>56.75797653198242</v>
       </c>
       <c r="C91" t="n">
         <v>77.47000122070312</v>
@@ -2580,11 +2592,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>57.90090942382812</v>
+        <v>57.90089797973633</v>
       </c>
       <c r="C92" t="n">
         <v>79.02999877929688</v>
@@ -2609,11 +2621,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>54.57469177246094</v>
+        <v>54.57470321655273</v>
       </c>
       <c r="C93" t="n">
         <v>74.48999786376953</v>
@@ -2638,11 +2650,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>55.86359786987305</v>
+        <v>55.86358261108398</v>
       </c>
       <c r="C94" t="n">
         <v>75.84999847412109</v>
@@ -2667,11 +2679,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>57.36604309082031</v>
+        <v>57.36605453491211</v>
       </c>
       <c r="C95" t="n">
         <v>77.88999938964844</v>
@@ -2696,11 +2708,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>59.41349792480469</v>
+        <v>59.41350173950195</v>
       </c>
       <c r="C96" t="n">
         <v>80.66999816894531</v>
@@ -2725,11 +2737,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>60.94139099121094</v>
+        <v>60.94143676757812</v>
       </c>
       <c r="C97" t="n">
         <v>82.33999633789062</v>
@@ -2754,11 +2766,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>56.87815093994141</v>
+        <v>56.87813949584961</v>
       </c>
       <c r="C98" t="n">
         <v>76.84999847412109</v>
@@ -2783,11 +2795,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>60.71198272705078</v>
+        <v>60.71197891235352</v>
       </c>
       <c r="C99" t="n">
         <v>82.02999877929688</v>
@@ -2812,11 +2824,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>58.90250396728516</v>
+        <v>58.90250015258789</v>
       </c>
       <c r="C100" t="n">
         <v>79.12999725341797</v>
@@ -2841,7 +2853,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2870,11 +2882,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>59.72130584716797</v>
+        <v>59.7213249206543</v>
       </c>
       <c r="C102" t="n">
         <v>80.23000335693359</v>
@@ -2899,11 +2911,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>60.61713790893555</v>
+        <v>60.61713027954102</v>
       </c>
       <c r="C103" t="n">
         <v>80.95999908447266</v>
@@ -2928,11 +2940,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>60.53476715087891</v>
+        <v>60.53477478027344</v>
       </c>
       <c r="C104" t="n">
         <v>80.84999847412109</v>
@@ -2957,11 +2969,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>70.00619506835938</v>
+        <v>70.00621032714844</v>
       </c>
       <c r="C105" t="n">
         <v>93.5</v>
@@ -2986,7 +2998,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3015,7 +3027,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3044,7 +3056,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3073,11 +3085,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>79.36842346191406</v>
+        <v>79.36846160888672</v>
       </c>
       <c r="C109" t="n">
         <v>104.9700012207031</v>
@@ -3102,7 +3114,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3131,11 +3143,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>86.76318359375</v>
+        <v>86.76317596435547</v>
       </c>
       <c r="C111" t="n">
         <v>114.75</v>
@@ -3160,7 +3172,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3189,11 +3201,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>81.30445098876953</v>
+        <v>81.30447387695312</v>
       </c>
       <c r="C113" t="n">
         <v>106.9800033569336</v>
@@ -3218,11 +3230,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>84.67884063720703</v>
+        <v>84.67881774902344</v>
       </c>
       <c r="C114" t="n">
         <v>111.4199981689453</v>
@@ -3247,11 +3259,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>84.90705108642578</v>
+        <v>84.90702819824219</v>
       </c>
       <c r="C115" t="n">
         <v>111.129997253418</v>
@@ -3276,11 +3288,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>89.41484069824219</v>
+        <v>89.41482543945312</v>
       </c>
       <c r="C116" t="n">
         <v>117.0299987792969</v>
@@ -3305,7 +3317,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3334,11 +3346,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>88.68750762939453</v>
+        <v>88.68753051757812</v>
       </c>
       <c r="C118" t="n">
         <v>115.4899978637695</v>
@@ -3363,11 +3375,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>94.94609832763672</v>
+        <v>94.94611358642578</v>
       </c>
       <c r="C119" t="n">
         <v>123.6399993896484</v>
@@ -3392,11 +3404,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>102.8096618652344</v>
+        <v>102.8096389770508</v>
       </c>
       <c r="C120" t="n">
         <v>133.8800048828125</v>
@@ -3421,11 +3433,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>102.0074462890625</v>
+        <v>102.0074615478516</v>
       </c>
       <c r="C121" t="n">
         <v>132.25</v>
@@ -3450,11 +3462,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>97.00157165527344</v>
+        <v>97.00156402587891</v>
       </c>
       <c r="C122" t="n">
         <v>125.7600021362305</v>
@@ -3479,11 +3491,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>95.73661041259766</v>
+        <v>95.73661804199219</v>
       </c>
       <c r="C123" t="n">
         <v>124.120002746582</v>
@@ -3508,11 +3520,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>103.4835510253906</v>
+        <v>103.4835586547852</v>
       </c>
       <c r="C124" t="n">
         <v>133.4299926757812</v>
@@ -3537,11 +3549,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>103.8403015136719</v>
+        <v>103.8403167724609</v>
       </c>
       <c r="C125" t="n">
         <v>133.8899993896484</v>
@@ -3566,11 +3578,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>102.9981460571289</v>
+        <v>102.9981842041016</v>
       </c>
       <c r="C126" t="n">
         <v>132.1199951171875</v>
@@ -3595,11 +3607,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>99.54461669921875</v>
+        <v>99.54463958740234</v>
       </c>
       <c r="C127" t="n">
         <v>127.6900024414062</v>
@@ -3624,11 +3636,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>107.7691955566406</v>
+        <v>107.7691879272461</v>
       </c>
       <c r="C128" t="n">
         <v>138.2400054931641</v>
@@ -3653,11 +3665,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>105.093505859375</v>
+        <v>105.0935287475586</v>
       </c>
       <c r="C129" t="n">
         <v>134.1199951171875</v>
@@ -3682,11 +3694,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>100.8308563232422</v>
+        <v>100.8308486938477</v>
       </c>
       <c r="C130" t="n">
         <v>128.6799926757812</v>
@@ -3711,11 +3723,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>95.60438537597656</v>
+        <v>95.60439300537109</v>
       </c>
       <c r="C131" t="n">
         <v>122.0100021362305</v>
@@ -3740,7 +3752,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3769,11 +3781,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>105.6200485229492</v>
+        <v>105.6200408935547</v>
       </c>
       <c r="C133" t="n">
         <v>134.0800018310547</v>
@@ -3798,11 +3810,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>108.3770980834961</v>
+        <v>108.3771286010742</v>
       </c>
       <c r="C134" t="n">
         <v>137.5800018310547</v>
@@ -3827,11 +3839,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>114.1512145996094</v>
+        <v>114.1512222290039</v>
       </c>
       <c r="C135" t="n">
         <v>144.9100036621094</v>
@@ -3856,11 +3868,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>116.3676223754883</v>
+        <v>116.3676147460938</v>
       </c>
       <c r="C136" t="n">
         <v>146.8300018310547</v>
@@ -3885,11 +3897,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>123.7144165039062</v>
+        <v>123.7143936157227</v>
       </c>
       <c r="C137" t="n">
         <v>156.1000061035156</v>
@@ -3914,11 +3926,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>122.3648147583008</v>
+        <v>122.3648071289062</v>
       </c>
       <c r="C138" t="n">
         <v>153.5099945068359</v>
@@ -3943,11 +3955,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>122.2770843505859</v>
+        <v>122.2770919799805</v>
       </c>
       <c r="C139" t="n">
         <v>153.3999938964844</v>
@@ -3972,11 +3984,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>119.2481155395508</v>
+        <v>119.2480926513672</v>
       </c>
       <c r="C140" t="n">
         <v>149.6000061035156</v>
@@ -4001,11 +4013,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>120.169807434082</v>
+        <v>120.1697616577148</v>
       </c>
       <c r="C141" t="n">
         <v>149.8699951171875</v>
@@ -4030,11 +4042,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>131.1467590332031</v>
+        <v>131.1467895507812</v>
       </c>
       <c r="C142" t="n">
         <v>163.5599975585938</v>
@@ -4059,11 +4071,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>132.9268188476562</v>
+        <v>132.9268341064453</v>
       </c>
       <c r="C143" t="n">
         <v>165.7799987792969</v>
@@ -4088,11 +4100,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>144.9149169921875</v>
+        <v>144.9149475097656</v>
       </c>
       <c r="C144" t="n">
         <v>179.8200073242188</v>
@@ -4117,11 +4129,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>152.7400970458984</v>
+        <v>152.7400817871094</v>
       </c>
       <c r="C145" t="n">
         <v>189.5299987792969</v>
@@ -4146,11 +4158,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>161.9030456542969</v>
+        <v>161.9030914306641</v>
       </c>
       <c r="C146" t="n">
         <v>200.8999938964844</v>
@@ -4175,11 +4187,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>146.8893280029297</v>
+        <v>146.8893890380859</v>
       </c>
       <c r="C147" t="n">
         <v>182.2700042724609</v>
@@ -4204,7 +4216,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4233,11 +4245,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>149.777587890625</v>
+        <v>149.7776184082031</v>
       </c>
       <c r="C149" t="n">
         <v>184.8000030517578</v>
@@ -4262,11 +4274,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>152.0424194335938</v>
+        <v>152.0424346923828</v>
       </c>
       <c r="C150" t="n">
         <v>186.5500030517578</v>
@@ -4291,11 +4303,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>159.0108642578125</v>
+        <v>159.0109405517578</v>
       </c>
       <c r="C151" t="n">
         <v>195.1000061035156</v>
@@ -4320,11 +4332,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>160.9832458496094</v>
+        <v>160.9832305908203</v>
       </c>
       <c r="C152" t="n">
         <v>197.5200042724609</v>
@@ -4349,11 +4361,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>164.4708709716797</v>
+        <v>164.4707946777344</v>
       </c>
       <c r="C153" t="n">
         <v>200.7700042724609</v>
@@ -4378,11 +4390,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>169.6972808837891</v>
+        <v>169.6972961425781</v>
       </c>
       <c r="C154" t="n">
         <v>207.1499938964844</v>
@@ -4407,11 +4419,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>144.0809020996094</v>
+        <v>144.0808868408203</v>
       </c>
       <c r="C155" t="n">
         <v>175.8800048828125</v>
@@ -4436,11 +4448,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>148.6017913818359</v>
+        <v>148.601806640625</v>
       </c>
       <c r="C156" t="n">
         <v>180.3200073242188</v>
@@ -4465,11 +4477,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>141.5968933105469</v>
+        <v>141.5969085693359</v>
       </c>
       <c r="C157" t="n">
         <v>171.8200073242188</v>
@@ -4494,11 +4506,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>151.2471618652344</v>
+        <v>151.2471466064453</v>
       </c>
       <c r="C158" t="n">
         <v>183.5299987792969</v>
@@ -4523,11 +4535,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>152.5739135742188</v>
+        <v>152.5739898681641</v>
       </c>
       <c r="C159" t="n">
         <v>185.1399993896484</v>
@@ -4552,11 +4564,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>159.3141174316406</v>
+        <v>159.3141937255859</v>
       </c>
       <c r="C160" t="n">
         <v>191.8899993896484</v>
@@ -4581,11 +4593,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>169.1192474365234</v>
+        <v>169.1192626953125</v>
       </c>
       <c r="C161" t="n">
         <v>203.6999969482422</v>
@@ -4610,7 +4622,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4639,11 +4651,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>173.8755798339844</v>
+        <v>173.8755187988281</v>
       </c>
       <c r="C163" t="n">
         <v>207.9700012207031</v>
@@ -4668,11 +4680,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>178.6577911376953</v>
+        <v>178.6577301025391</v>
       </c>
       <c r="C164" t="n">
         <v>213.6900024414062</v>
@@ -4697,7 +4709,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4726,11 +4738,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>195.1673431396484</v>
+        <v>195.1673583984375</v>
       </c>
       <c r="C166" t="n">
         <v>232.0200042724609</v>
@@ -4755,11 +4767,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>197.3207244873047</v>
+        <v>197.3207092285156</v>
       </c>
       <c r="C167" t="n">
         <v>234.5800018310547</v>
@@ -4784,11 +4796,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>185.4855194091797</v>
+        <v>185.4855041503906</v>
       </c>
       <c r="C168" t="n">
         <v>220.5099945068359</v>
@@ -4813,7 +4825,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4842,11 +4854,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>193.0971221923828</v>
+        <v>193.0971069335938</v>
       </c>
       <c r="C170" t="n">
         <v>228.1000061035156</v>
@@ -4871,11 +4883,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>184.4114990234375</v>
+        <v>184.4115600585938</v>
       </c>
       <c r="C171" t="n">
         <v>217.8399963378906</v>
@@ -4900,11 +4912,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>159.1160736083984</v>
+        <v>159.1160430908203</v>
       </c>
       <c r="C172" t="n">
         <v>186.7100067138672</v>
@@ -4929,11 +4941,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>187.3412780761719</v>
+        <v>187.3412628173828</v>
       </c>
       <c r="C173" t="n">
         <v>219.8300018310547</v>
@@ -4958,11 +4970,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>211.757080078125</v>
+        <v>211.7570343017578</v>
       </c>
       <c r="C174" t="n">
         <v>248.4799957275391</v>
@@ -4987,11 +4999,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>214.7618255615234</v>
+        <v>214.7618103027344</v>
       </c>
       <c r="C175" t="n">
         <v>250.5099945068359</v>
@@ -5016,11 +5028,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>227.6041107177734</v>
+        <v>227.6041412353516</v>
       </c>
       <c r="C176" t="n">
         <v>265.489990234375</v>
@@ -5045,11 +5057,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>244.3643341064453</v>
+        <v>244.3643035888672</v>
       </c>
       <c r="C177" t="n">
         <v>285.0400085449219</v>
@@ -5074,11 +5086,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>239.3358306884766</v>
+        <v>239.3358001708984</v>
       </c>
       <c r="C178" t="n">
         <v>277.7099914550781</v>
@@ -5103,11 +5115,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>229.8558654785156</v>
+        <v>229.8558197021484</v>
       </c>
       <c r="C179" t="n">
         <v>266.7099914550781</v>
@@ -5132,11 +5144,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>239.0772857666016</v>
+        <v>239.0773010253906</v>
       </c>
       <c r="C180" t="n">
         <v>277.4100036621094</v>
@@ -5161,11 +5173,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>230.1646575927734</v>
+        <v>230.1645965576172</v>
       </c>
       <c r="C181" t="n">
         <v>265.6199951171875</v>
@@ -5190,11 +5202,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>234.6705017089844</v>
+        <v>234.6705322265625</v>
       </c>
       <c r="C182" t="n">
         <v>270.8200073242188</v>
@@ -5219,11 +5231,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>223.8563537597656</v>
+        <v>223.8563385009766</v>
       </c>
       <c r="C183" t="n">
         <v>258.3399963378906</v>
@@ -5248,7 +5260,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5277,11 +5289,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>282.2235107421875</v>
+        <v>282.2235412597656</v>
       </c>
       <c r="C185" t="n">
         <v>323.6700134277344</v>
@@ -5306,11 +5318,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>278.0731201171875</v>
+        <v>278.0730895996094</v>
       </c>
       <c r="C186" t="n">
         <v>318.9100036621094</v>
@@ -5335,7 +5347,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5364,11 +5376,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>287.6653137207031</v>
+        <v>287.6653442382812</v>
       </c>
       <c r="C188" t="n">
         <v>328.1900024414062</v>
@@ -5393,11 +5405,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>285.9034729003906</v>
+        <v>285.9035034179688</v>
       </c>
       <c r="C189" t="n">
         <v>326.1799926757812</v>
@@ -5422,11 +5434,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>289.1895751953125</v>
+        <v>289.1896057128906</v>
       </c>
       <c r="C190" t="n">
         <v>328.260009765625</v>
@@ -5451,7 +5463,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5480,11 +5492,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>352.9282531738281</v>
+        <v>352.9282836914062</v>
       </c>
       <c r="C192" t="n">
         <v>400.6099853515625</v>
@@ -5509,11 +5521,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>367.12646484375</v>
+        <v>367.1264038085938</v>
       </c>
       <c r="C193" t="n">
         <v>415.010009765625</v>
@@ -5538,11 +5550,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>324.6380615234375</v>
+        <v>324.6381530761719</v>
       </c>
       <c r="C194" t="n">
         <v>366.9800109863281</v>
@@ -5567,11 +5579,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>279.3897705078125</v>
+        <v>279.3897399902344</v>
       </c>
       <c r="C195" t="n">
         <v>315.8299865722656</v>
@@ -5596,7 +5608,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5625,7 +5637,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5654,7 +5666,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5683,11 +5695,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>245.6306457519531</v>
+        <v>245.6306610107422</v>
       </c>
       <c r="C199" t="n">
         <v>274.2699890136719</v>
@@ -5712,11 +5724,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>269.5157165527344</v>
+        <v>269.5157775878906</v>
       </c>
       <c r="C200" t="n">
         <v>300.9400024414062</v>
@@ -5741,11 +5753,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>259.9884948730469</v>
+        <v>259.9884643554688</v>
       </c>
       <c r="C201" t="n">
         <v>288.4200134277344</v>
@@ -5770,11 +5782,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>248.7387237548828</v>
+        <v>248.7386779785156</v>
       </c>
       <c r="C202" t="n">
         <v>275.9400024414062</v>
@@ -5799,7 +5811,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5828,7 +5840,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5857,7 +5869,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5886,11 +5898,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>293.9822082519531</v>
+        <v>293.982177734375</v>
       </c>
       <c r="C206" t="n">
         <v>324.1700134277344</v>
@@ -5915,11 +5927,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>268.9251098632812</v>
+        <v>268.9251403808594</v>
       </c>
       <c r="C207" t="n">
         <v>296.5400085449219</v>
@@ -5944,11 +5956,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>269.5754699707031</v>
+        <v>269.5755004882812</v>
       </c>
       <c r="C208" t="n">
         <v>295.1199951171875</v>
@@ -5973,11 +5985,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>274.5263366699219</v>
+        <v>274.5263671875</v>
       </c>
       <c r="C209" t="n">
         <v>300.5400085449219</v>
@@ -6002,11 +6014,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>260.7796020507812</v>
+        <v>260.7796325683594</v>
       </c>
       <c r="C210" t="n">
         <v>283.4500122070312</v>
@@ -6031,11 +6043,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>285.7949523925781</v>
+        <v>285.794921875</v>
       </c>
       <c r="C211" t="n">
         <v>310.6400146484375</v>
@@ -6060,11 +6072,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>307.1394653320312</v>
+        <v>307.1393737792969</v>
       </c>
       <c r="C212" t="n">
         <v>333.8399963378906</v>
@@ -6089,11 +6101,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>305.8230285644531</v>
+        <v>305.8230590820312</v>
       </c>
       <c r="C213" t="n">
         <v>330.2999877929688</v>
@@ -6118,11 +6130,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>279.7684020996094</v>
+        <v>279.7684326171875</v>
       </c>
       <c r="C214" t="n">
         <v>302.1600036621094</v>
@@ -6147,7 +6159,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6176,11 +6188,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>292.2078247070312</v>
+        <v>292.2077941894531</v>
       </c>
       <c r="C216" t="n">
         <v>313.489990234375</v>
@@ -6205,11 +6217,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>323.0234375</v>
+        <v>323.0233764648438</v>
       </c>
       <c r="C217" t="n">
         <v>346.5499877929688</v>
@@ -6234,7 +6246,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6263,11 +6275,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>354.7712097167969</v>
+        <v>354.7711791992188</v>
       </c>
       <c r="C219" t="n">
         <v>380.6099853515625</v>
@@ -6292,7 +6304,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6321,11 +6333,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>313.3937072753906</v>
+        <v>313.3937377929688</v>
       </c>
       <c r="C221" t="n">
         <v>334.2200012207031</v>
@@ -6350,7 +6362,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6379,11 +6391,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>325.0332946777344</v>
+        <v>325.0332641601562</v>
       </c>
       <c r="C223" t="n">
         <v>344.239990234375</v>
@@ -6408,11 +6420,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>347.61865234375</v>
+        <v>347.6187133789062</v>
       </c>
       <c r="C224" t="n">
         <v>368.1600036621094</v>
@@ -6437,7 +6449,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6466,11 +6478,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>384.9158935546875</v>
+        <v>384.9158630371094</v>
       </c>
       <c r="C226" t="n">
         <v>405.2000122070312</v>
@@ -6495,11 +6507,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>374.0390319824219</v>
+        <v>374.0390625</v>
       </c>
       <c r="C227" t="n">
         <v>393.75</v>
@@ -6524,7 +6536,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6553,11 +6565,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>371.4631958007812</v>
+        <v>371.4631652832031</v>
       </c>
       <c r="C229" t="n">
         <v>388.989990234375</v>
@@ -6582,11 +6594,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>393.4173583984375</v>
+        <v>393.4173889160156</v>
       </c>
       <c r="C230" t="n">
         <v>411.9800109863281</v>
@@ -6611,7 +6623,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6640,11 +6652,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>352.197998046875</v>
+        <v>352.1979675292969</v>
       </c>
       <c r="C232" t="n">
         <v>366.489990234375</v>
@@ -6669,7 +6681,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6698,11 +6710,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>353.9278259277344</v>
+        <v>353.9278564453125</v>
       </c>
       <c r="C234" t="n">
         <v>368.2900085449219</v>
@@ -6727,11 +6739,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>354.5318298339844</v>
+        <v>354.5317993164062</v>
       </c>
       <c r="C235" t="n">
         <v>366.6400146484375</v>
@@ -6756,11 +6768,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>355.373046875</v>
+        <v>355.3730773925781</v>
       </c>
       <c r="C236" t="n">
         <v>367.510009765625</v>
@@ -6785,7 +6797,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6814,11 +6826,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>394.031494140625</v>
+        <v>394.0315246582031</v>
       </c>
       <c r="C238" t="n">
         <v>405.1900024414062</v>
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6872,11 +6884,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>347.0908508300781</v>
+        <v>347.0908203125</v>
       </c>
       <c r="C240" t="n">
         <v>356.9200134277344</v>
@@ -6901,11 +6913,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>336.7881469726562</v>
+        <v>336.7881164550781</v>
       </c>
       <c r="C241" t="n">
         <v>344.1000061035156</v>
@@ -6930,7 +6942,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6959,11 +6971,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>372.6300048828125</v>
+        <v>372.6299743652344</v>
       </c>
       <c r="C243" t="n">
         <v>380.7200012207031</v>
@@ -6988,7 +7000,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7017,7 +7029,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7046,7 +7058,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7075,7 +7087,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7104,7 +7116,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7133,7 +7145,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7162,32 +7174,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>296.7200012207031</v>
+        <v>292.1799926757812</v>
       </c>
       <c r="C250" t="n">
-        <v>296.7200012207031</v>
+        <v>292.1799926757812</v>
       </c>
       <c r="D250" t="n">
-        <v>69991500</v>
+        <v>77045300</v>
       </c>
       <c r="E250" t="n">
         <v>14.29</v>
       </c>
       <c r="F250" t="n">
-        <v>20.76417083419896</v>
+        <v>20.4464655476404</v>
       </c>
       <c r="G250" t="n">
         <v>997689626</v>
       </c>
       <c r="H250" t="n">
-        <v>296034467044.6028</v>
+        <v>291504947617.3829</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07015358100957141</v>
+        <v>0.07722371566485547</v>
       </c>
     </row>
   </sheetData>
@@ -7219,75 +7231,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39573</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39663</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40059</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7323,13 +7335,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39664</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39754</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40150</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7365,13 +7377,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39846</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39936</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40332</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7407,13 +7419,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39937</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40027</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40059</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7449,13 +7461,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40028</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40150</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7491,13 +7503,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40300</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40332</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7533,13 +7545,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40301</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40423</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7575,13 +7587,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40392</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40514</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7617,13 +7629,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40573</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="I10" t="n">
         <v>2.01</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="K10" t="n">
@@ -7663,13 +7675,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40696</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7696,7 +7708,7 @@
       <c r="I11" t="n">
         <v>2.08</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40696</v>
       </c>
       <c r="K11" t="n">
@@ -7709,13 +7721,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40665</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7742,7 +7754,7 @@
       <c r="I12" t="n">
         <v>2.22</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="K12" t="n">
@@ -7755,13 +7767,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40846</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40876</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7788,7 +7800,7 @@
       <c r="I13" t="n">
         <v>2.31</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40876</v>
       </c>
       <c r="K13" t="n">
@@ -7801,13 +7813,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40937</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40990</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7834,7 +7846,7 @@
       <c r="I14" t="n">
         <v>2.47</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40990</v>
       </c>
       <c r="K14" t="n">
@@ -7847,13 +7859,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40938</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41028</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41053</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7880,7 +7892,7 @@
       <c r="I15" t="n">
         <v>2.65</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41053</v>
       </c>
       <c r="K15" t="n">
@@ -7893,13 +7905,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41119</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41143</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7926,7 +7938,7 @@
       <c r="I16" t="n">
         <v>2.8</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41143</v>
       </c>
       <c r="K16" t="n">
@@ -7939,13 +7951,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41120</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41210</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7972,7 +7984,7 @@
       <c r="I17" t="n">
         <v>2.83</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="K17" t="n">
@@ -7985,13 +7997,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41211</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41308</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41361</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8018,7 +8030,7 @@
       <c r="I18" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41361</v>
       </c>
       <c r="K18" t="n">
@@ -8031,13 +8043,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41309</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41399</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41423</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8064,7 +8076,7 @@
       <c r="I19" t="n">
         <v>3.15</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41423</v>
       </c>
       <c r="K19" t="n">
@@ -8077,13 +8089,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41400</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41490</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41514</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8110,7 +8122,7 @@
       <c r="I20" t="n">
         <v>3.38</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41514</v>
       </c>
       <c r="K20" t="n">
@@ -8123,13 +8135,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41491</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41581</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41605</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8156,7 +8168,7 @@
       <c r="I21" t="n">
         <v>3.7</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41605</v>
       </c>
       <c r="K21" t="n">
@@ -8169,13 +8181,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41582</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41672</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41725</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8202,7 +8214,7 @@
       <c r="I22" t="n">
         <v>3.75</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41725</v>
       </c>
       <c r="K22" t="n">
@@ -8215,13 +8227,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41673</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41763</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41787</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8248,7 +8260,7 @@
       <c r="I23" t="n">
         <v>3.92</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41787</v>
       </c>
       <c r="K23" t="n">
@@ -8261,13 +8273,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41764</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41854</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41878</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8294,7 +8306,7 @@
       <c r="I24" t="n">
         <v>4.2</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41878</v>
       </c>
       <c r="K24" t="n">
@@ -8307,13 +8319,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41855</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41945</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41968</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8340,7 +8352,7 @@
       <c r="I25" t="n">
         <v>4.399999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41968</v>
       </c>
       <c r="K25" t="n">
@@ -8353,13 +8365,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41946</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42089</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8386,7 +8398,7 @@
       <c r="I26" t="n">
         <v>4.720000000000001</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42089</v>
       </c>
       <c r="K26" t="n">
@@ -8399,13 +8411,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42037</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42127</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42151</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8432,7 +8444,7 @@
       <c r="I27" t="n">
         <v>4.93</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42151</v>
       </c>
       <c r="K27" t="n">
@@ -8445,13 +8457,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42128</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42218</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42241</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8478,7 +8490,7 @@
       <c r="I28" t="n">
         <v>5.14</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42241</v>
       </c>
       <c r="K28" t="n">
@@ -8491,13 +8503,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42219</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42332</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8524,7 +8536,7 @@
       <c r="I29" t="n">
         <v>5.34</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42332</v>
       </c>
       <c r="K29" t="n">
@@ -8537,13 +8549,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42310</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42453</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8570,7 +8582,7 @@
       <c r="I30" t="n">
         <v>5.459999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42453</v>
       </c>
       <c r="K30" t="n">
@@ -8583,13 +8595,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42514</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8616,7 +8628,7 @@
       <c r="I31" t="n">
         <v>5.69</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42514</v>
       </c>
       <c r="K31" t="n">
@@ -8629,13 +8641,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42492</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42605</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8662,7 +8674,7 @@
       <c r="I32" t="n">
         <v>5.93</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42605</v>
       </c>
       <c r="K32" t="n">
@@ -8675,13 +8687,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42673</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8708,7 +8720,7 @@
       <c r="I33" t="n">
         <v>6.180000000000001</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="K33" t="n">
@@ -8721,13 +8733,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42817</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8754,7 +8766,7 @@
       <c r="I34" t="n">
         <v>6.449999999999999</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42817</v>
       </c>
       <c r="K34" t="n">
@@ -8767,13 +8779,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42765</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8800,7 +8812,7 @@
       <c r="I35" t="n">
         <v>6.68</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="K35" t="n">
@@ -8813,13 +8825,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42969</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8846,7 +8858,7 @@
       <c r="I36" t="n">
         <v>6.96</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42969</v>
       </c>
       <c r="K36" t="n">
@@ -8859,13 +8871,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43037</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8892,7 +8904,7 @@
       <c r="I37" t="n">
         <v>7.199999999999999</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="K37" t="n">
@@ -8905,13 +8917,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43038</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43128</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43181</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8938,7 +8950,7 @@
       <c r="I38" t="n">
         <v>7.28</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43181</v>
       </c>
       <c r="K38" t="n">
@@ -8951,13 +8963,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43129</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43219</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8984,7 +8996,7 @@
       <c r="I39" t="n">
         <v>7.69</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="K39" t="n">
@@ -8997,13 +9009,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43310</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43333</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9030,7 +9042,7 @@
       <c r="I40" t="n">
         <v>8.49</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43333</v>
       </c>
       <c r="K40" t="n">
@@ -9043,13 +9055,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43311</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43401</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9076,7 +9088,7 @@
       <c r="I41" t="n">
         <v>9.16</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="K41" t="n">
@@ -9089,13 +9101,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43402</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43499</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43552</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9122,7 +9134,7 @@
       <c r="I42" t="n">
         <v>9.73</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43552</v>
       </c>
       <c r="K42" t="n">
@@ -9135,13 +9147,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43500</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43590</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43614</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9168,7 +9180,7 @@
       <c r="I43" t="n">
         <v>9.92</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43614</v>
       </c>
       <c r="K43" t="n">
@@ -9181,13 +9193,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43591</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43681</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43704</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9214,7 +9226,7 @@
       <c r="I44" t="n">
         <v>10.04</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43704</v>
       </c>
       <c r="K44" t="n">
@@ -9227,13 +9239,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43682</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43772</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43795</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9260,7 +9272,7 @@
       <c r="I45" t="n">
         <v>10.06</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43795</v>
       </c>
       <c r="K45" t="n">
@@ -9273,13 +9285,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43773</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43863</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43915</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9306,7 +9318,7 @@
       <c r="I46" t="n">
         <v>10.25</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43915</v>
       </c>
       <c r="K46" t="n">
@@ -9319,13 +9331,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43864</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43954</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43978</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9352,7 +9364,7 @@
       <c r="I47" t="n">
         <v>10.06</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43978</v>
       </c>
       <c r="K47" t="n">
@@ -9365,13 +9377,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43955</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44045</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44068</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9398,7 +9410,7 @@
       <c r="I48" t="n">
         <v>10.91</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44068</v>
       </c>
       <c r="K48" t="n">
@@ -9411,13 +9423,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44046</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44159</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9444,7 +9456,7 @@
       <c r="I49" t="n">
         <v>11.56</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44159</v>
       </c>
       <c r="K49" t="n">
@@ -9457,13 +9469,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44137</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44279</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9490,7 +9502,7 @@
       <c r="I50" t="n">
         <v>11.94</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44279</v>
       </c>
       <c r="K50" t="n">
@@ -9503,13 +9515,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44341</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9536,7 +9548,7 @@
       <c r="I51" t="n">
         <v>13.72</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44341</v>
       </c>
       <c r="K51" t="n">
@@ -9549,13 +9561,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44319</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44432</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9582,7 +9594,7 @@
       <c r="I52" t="n">
         <v>14.23</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44432</v>
       </c>
       <c r="K52" t="n">
@@ -9595,13 +9607,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44523</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9628,7 +9640,7 @@
       <c r="I53" t="n">
         <v>14.97</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44523</v>
       </c>
       <c r="K53" t="n">
@@ -9641,13 +9653,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44643</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9674,7 +9686,7 @@
       <c r="I54" t="n">
         <v>15.53</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44643</v>
       </c>
       <c r="K54" t="n">
@@ -9687,13 +9699,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44705</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9720,7 +9732,7 @@
       <c r="I55" t="n">
         <v>15.76</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44705</v>
       </c>
       <c r="K55" t="n">
@@ -9733,13 +9745,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44683</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44796</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9766,7 +9778,7 @@
       <c r="I56" t="n">
         <v>16.28</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44796</v>
       </c>
       <c r="K56" t="n">
@@ -9779,13 +9791,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44864</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9812,7 +9824,7 @@
       <c r="I57" t="n">
         <v>16.6</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="K57" t="n">
@@ -9825,13 +9837,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45000</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9858,7 +9870,7 @@
       <c r="I58" t="n">
         <v>16.69</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45000</v>
       </c>
       <c r="K58" t="n">
@@ -9871,13 +9883,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44956</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45069</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9904,7 +9916,7 @@
       <c r="I59" t="n">
         <v>16.42</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45069</v>
       </c>
       <c r="K59" t="n">
@@ -9917,13 +9929,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45160</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9950,7 +9962,7 @@
       <c r="I60" t="n">
         <v>16.02</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45160</v>
       </c>
       <c r="K60" t="n">
@@ -9963,13 +9975,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45228</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9996,7 +10008,7 @@
       <c r="I61" t="n">
         <v>15.59</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="K61" t="n">
@@ -10009,13 +10021,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45319</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10042,7 +10054,7 @@
       <c r="I62" t="n">
         <v>15.11</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="K62" t="n">
@@ -10055,13 +10067,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45320</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45410</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10088,7 +10100,7 @@
       <c r="I63" t="n">
         <v>14.92</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="K63" t="n">
@@ -10101,13 +10113,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45501</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45524</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10134,7 +10146,7 @@
       <c r="I64" t="n">
         <v>14.87</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45524</v>
       </c>
       <c r="K64" t="n">
@@ -10147,13 +10159,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45502</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45592</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45615</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10180,7 +10192,7 @@
       <c r="I65" t="n">
         <v>14.73</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45615</v>
       </c>
       <c r="K65" t="n">
@@ -10193,13 +10205,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45593</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45690</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10226,7 +10238,7 @@
       <c r="I66" t="n">
         <v>14.91</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="K66" t="n">
@@ -10239,13 +10251,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45691</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45781</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10272,7 +10284,7 @@
       <c r="I67" t="n">
         <v>14.73</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="K67" t="n">
@@ -10285,13 +10297,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45782</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45872</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10318,7 +10330,7 @@
       <c r="I68" t="n">
         <v>14.71</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="K68" t="n">
@@ -10331,13 +10343,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45873</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10364,7 +10376,7 @@
       <c r="I69" t="n">
         <v>14.66</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="K69" t="n">
@@ -10377,13 +10389,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45964</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10410,7 +10422,7 @@
       <c r="I70" t="n">
         <v>14.23</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="K70" t="n">
@@ -10423,13 +10435,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46055</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46169</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10456,7 +10468,7 @@
       <c r="I71" t="n">
         <v>14.08</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46169</v>
       </c>
       <c r="K71" t="n">
@@ -10469,13 +10481,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46146</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46236</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46259</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10502,7 +10514,7 @@
       <c r="I72" t="n">
         <v>14.29</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46259</v>
       </c>
       <c r="K72" t="n">
@@ -10539,52 +10551,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40053</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40059</v>
       </c>
       <c r="C2" t="n">
@@ -10613,10 +10625,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40144</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40150</v>
       </c>
       <c r="C3" t="n">
@@ -10645,10 +10657,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40259</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40262</v>
       </c>
       <c r="C4" t="n">
@@ -10677,10 +10689,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40326</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40332</v>
       </c>
       <c r="C5" t="n">
@@ -10709,10 +10721,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40417</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40423</v>
       </c>
       <c r="C6" t="n">
@@ -10741,10 +10753,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40508</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40514</v>
       </c>
       <c r="C7" t="n">
@@ -10773,10 +10785,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40616</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40626</v>
       </c>
       <c r="C8" t="n">
@@ -10805,10 +10817,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40690</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40696</v>
       </c>
       <c r="C9" t="n">
@@ -10837,10 +10849,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40780</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="C10" t="n">
@@ -10869,10 +10881,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40868</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40876</v>
       </c>
       <c r="C11" t="n">
@@ -10901,10 +10913,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40982</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40990</v>
       </c>
       <c r="C12" t="n">
@@ -10933,10 +10945,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41045</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41053</v>
       </c>
       <c r="C13" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41136</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41143</v>
       </c>
       <c r="C14" t="n">
@@ -10997,10 +11009,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41226</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41234</v>
       </c>
       <c r="C15" t="n">
@@ -11029,10 +11041,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41344</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41361</v>
       </c>
       <c r="C16" t="n">
@@ -11061,10 +11073,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41415</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41423</v>
       </c>
       <c r="C17" t="n">
@@ -11093,10 +11105,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41506</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41514</v>
       </c>
       <c r="C18" t="n">
@@ -11125,10 +11137,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41597</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41605</v>
       </c>
       <c r="C19" t="n">
@@ -11157,10 +11169,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41708</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41725</v>
       </c>
       <c r="C20" t="n">
@@ -11189,10 +11201,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41779</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41787</v>
       </c>
       <c r="C21" t="n">
@@ -11221,10 +11233,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41870</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41878</v>
       </c>
       <c r="C22" t="n">
@@ -11253,10 +11265,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41961</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41968</v>
       </c>
       <c r="C23" t="n">
@@ -11285,10 +11297,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42069</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42089</v>
       </c>
       <c r="C24" t="n">
@@ -11317,10 +11329,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42143</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42151</v>
       </c>
       <c r="C25" t="n">
@@ -11349,10 +11361,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42234</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42241</v>
       </c>
       <c r="C26" t="n">
@@ -11381,10 +11393,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42325</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42332</v>
       </c>
       <c r="C27" t="n">
@@ -11413,10 +11425,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42433</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42453</v>
       </c>
       <c r="C28" t="n">
@@ -11445,10 +11457,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42507</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42514</v>
       </c>
       <c r="C29" t="n">
@@ -11477,10 +11489,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42598</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42605</v>
       </c>
       <c r="C30" t="n">
@@ -11509,10 +11521,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42689</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42696</v>
       </c>
       <c r="C31" t="n">
@@ -11541,10 +11553,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42797</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42817</v>
       </c>
       <c r="C32" t="n">
@@ -11573,10 +11585,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42871</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="C33" t="n">
@@ -11605,10 +11617,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42962</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42969</v>
       </c>
       <c r="C34" t="n">
@@ -11637,10 +11649,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43053</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43060</v>
       </c>
       <c r="C35" t="n">
@@ -11669,10 +11681,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43161</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43181</v>
       </c>
       <c r="C36" t="n">
@@ -11701,10 +11713,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43235</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="C37" t="n">
@@ -11733,10 +11745,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43326</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43333</v>
       </c>
       <c r="C38" t="n">
@@ -11765,10 +11777,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43417</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="C39" t="n">
@@ -11797,10 +11809,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43532</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43552</v>
       </c>
       <c r="C40" t="n">
@@ -11829,10 +11841,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43606</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43614</v>
       </c>
       <c r="C41" t="n">
@@ -11861,10 +11873,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43697</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43704</v>
       </c>
       <c r="C42" t="n">
@@ -11893,10 +11905,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43788</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43795</v>
       </c>
       <c r="C43" t="n">
@@ -11925,10 +11937,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43896</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43915</v>
       </c>
       <c r="C44" t="n">
@@ -11957,10 +11969,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43970</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43978</v>
       </c>
       <c r="C45" t="n">
@@ -11989,10 +12001,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44061</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44068</v>
       </c>
       <c r="C46" t="n">
@@ -12021,10 +12033,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44152</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44159</v>
       </c>
       <c r="C47" t="n">
@@ -12053,10 +12065,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44260</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44279</v>
       </c>
       <c r="C48" t="n">
@@ -12085,10 +12097,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44334</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44341</v>
       </c>
       <c r="C49" t="n">
@@ -12117,10 +12129,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44425</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44432</v>
       </c>
       <c r="C50" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44516</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44523</v>
       </c>
       <c r="C51" t="n">
@@ -12181,10 +12193,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44624</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44643</v>
       </c>
       <c r="C52" t="n">
@@ -12213,10 +12225,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44698</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44705</v>
       </c>
       <c r="C53" t="n">
@@ -12245,10 +12257,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44789</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44796</v>
       </c>
       <c r="C54" t="n">
@@ -12277,10 +12289,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44880</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44887</v>
       </c>
       <c r="C55" t="n">
@@ -12309,10 +12321,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45000</v>
       </c>
       <c r="C56" t="n">
@@ -12341,10 +12353,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45062</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45069</v>
       </c>
       <c r="C57" t="n">
@@ -12373,10 +12385,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45153</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45160</v>
       </c>
       <c r="C58" t="n">
@@ -12405,10 +12417,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45244</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45251</v>
       </c>
       <c r="C59" t="n">
@@ -12437,10 +12449,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45350</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="C60" t="n">
@@ -12469,10 +12481,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45426</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45433</v>
       </c>
       <c r="C61" t="n">
@@ -12501,10 +12513,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45517</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45524</v>
       </c>
       <c r="C62" t="n">
@@ -12533,10 +12545,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45608</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45615</v>
       </c>
       <c r="C63" t="n">
@@ -12565,10 +12577,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45721</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45737</v>
       </c>
       <c r="C64" t="n">
@@ -12597,10 +12609,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45797</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="C65" t="n">
@@ -12629,10 +12641,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45888</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45895</v>
       </c>
       <c r="C66" t="n">
@@ -12661,10 +12673,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45979</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="C67" t="n">
@@ -12693,10 +12705,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46099</v>
       </c>
       <c r="C68" t="n">
@@ -12725,10 +12737,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46161</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46169</v>
       </c>
       <c r="C69" t="n">
@@ -12757,10 +12769,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46252</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46259</v>
       </c>
       <c r="C70" t="n">
@@ -12807,12 +12819,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/HD.xlsx
+++ b/salidas/empresas/HD.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>24.06368255615234</v>
+        <v>24.06368064880371</v>
       </c>
       <c r="C2" t="n">
         <v>40.54999923706055</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>25.0131778717041</v>
+        <v>25.01317405700684</v>
       </c>
       <c r="C3" t="n">
         <v>42.15000152587891</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>25.19259071350098</v>
+        <v>25.19259452819824</v>
       </c>
       <c r="C4" t="n">
         <v>42.29999923706055</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>23.78109550476074</v>
+        <v>23.78108406066895</v>
       </c>
       <c r="C5" t="n">
         <v>39.93000030517578</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>22.7031192779541</v>
+        <v>22.70311164855957</v>
       </c>
       <c r="C6" t="n">
         <v>38.11999893188477</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>21.40113258361816</v>
+        <v>21.4011402130127</v>
       </c>
       <c r="C7" t="n">
         <v>35.79000091552734</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>21.78248023986816</v>
+        <v>21.78247451782227</v>
       </c>
       <c r="C10" t="n">
         <v>36.27000045776367</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>22.41907691955566</v>
+        <v>22.41908264160156</v>
       </c>
       <c r="C11" t="n">
         <v>37.33000183105469</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>24.26391983032227</v>
+        <v>24.2639045715332</v>
       </c>
       <c r="C13" t="n">
         <v>40.15999984741211</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>24.61433601379395</v>
+        <v>24.61433029174805</v>
       </c>
       <c r="C14" t="n">
         <v>40.7400016784668</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>23.91952705383301</v>
+        <v>23.91952514648438</v>
       </c>
       <c r="C15" t="n">
         <v>39.59000015258789</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>22.3275260925293</v>
+        <v>22.3275203704834</v>
       </c>
       <c r="C16" t="n">
         <v>36.7400016784668</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>23.01423835754395</v>
+        <v>23.01424217224121</v>
       </c>
       <c r="C17" t="n">
         <v>37.86999893188477</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>23.62196922302246</v>
+        <v>23.62196159362793</v>
       </c>
       <c r="C18" t="n">
         <v>38.86999893188477</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>24.04963111877441</v>
+        <v>24.04961967468262</v>
       </c>
       <c r="C19" t="n">
         <v>39.34999847412109</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>22.71727561950684</v>
+        <v>22.71727752685547</v>
       </c>
       <c r="C20" t="n">
         <v>37.16999816894531</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>23.56441497802734</v>
+        <v>23.56442451477051</v>
       </c>
       <c r="C21" t="n">
         <v>38.31000137329102</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>19.95378303527832</v>
+        <v>19.95379257202148</v>
       </c>
       <c r="C22" t="n">
         <v>32.43999862670898</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>19.38174438476562</v>
+        <v>19.38175201416016</v>
       </c>
       <c r="C23" t="n">
         <v>31.51000022888184</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.71218109130859</v>
+        <v>17.71217918395996</v>
       </c>
       <c r="C24" t="n">
         <v>28.55999946594238</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>17.50380897521973</v>
+        <v>17.50381278991699</v>
       </c>
       <c r="C28" t="n">
         <v>27.96999931335449</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>18.02323150634766</v>
+        <v>18.02323341369629</v>
       </c>
       <c r="C29" t="n">
         <v>28.79999923706055</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>17.1220703125</v>
+        <v>17.12206840515137</v>
       </c>
       <c r="C30" t="n">
         <v>27.36000061035156</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>15.0375394821167</v>
+        <v>15.03754711151123</v>
       </c>
       <c r="C32" t="n">
         <v>23.82999992370605</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>17.11364936828613</v>
+        <v>17.1136474609375</v>
       </c>
       <c r="C33" t="n">
         <v>27.1200008392334</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>16.47415351867676</v>
+        <v>16.47415161132812</v>
       </c>
       <c r="C34" t="n">
         <v>25.88999938964844</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>15.01063442230225</v>
+        <v>15.01063632965088</v>
       </c>
       <c r="C35" t="n">
         <v>23.59000015258789</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>14.70520687103271</v>
+        <v>14.70520496368408</v>
       </c>
       <c r="C36" t="n">
         <v>23.11000061035156</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.80498504638672</v>
+        <v>14.80498218536377</v>
       </c>
       <c r="C37" t="n">
         <v>23.02000045776367</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>13.84671497344971</v>
+        <v>13.84671592712402</v>
       </c>
       <c r="C38" t="n">
         <v>21.53000068664551</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>13.4351110458374</v>
+        <v>13.43510818481445</v>
       </c>
       <c r="C39" t="n">
         <v>20.88999938964844</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>15.34163761138916</v>
+        <v>15.34163284301758</v>
       </c>
       <c r="C40" t="n">
         <v>23.55999946594238</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>17.13886451721191</v>
+        <v>17.13887023925781</v>
       </c>
       <c r="C41" t="n">
         <v>26.31999969482422</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>15.08116436004639</v>
+        <v>15.08115863800049</v>
       </c>
       <c r="C42" t="n">
         <v>23.15999984741211</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>15.52947998046875</v>
+        <v>15.52948093414307</v>
       </c>
       <c r="C43" t="n">
         <v>23.6299991607666</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>17.934814453125</v>
+        <v>17.93481636047363</v>
       </c>
       <c r="C45" t="n">
         <v>27.29000091552734</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>17.65318870544434</v>
+        <v>17.65317916870117</v>
       </c>
       <c r="C46" t="n">
         <v>26.63999938964844</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>16.62606811523438</v>
+        <v>16.62606048583984</v>
       </c>
       <c r="C47" t="n">
         <v>25.09000015258789</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.13028907775879</v>
+        <v>18.13029861450195</v>
       </c>
       <c r="C48" t="n">
         <v>27.36000061035156</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>19.32962799072266</v>
+        <v>19.32962608337402</v>
       </c>
       <c r="C49" t="n">
         <v>28.93000030517578</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>18.71492958068848</v>
+        <v>18.71493339538574</v>
       </c>
       <c r="C50" t="n">
         <v>28.01000022888184</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>20.84633636474609</v>
+        <v>20.84633445739746</v>
       </c>
       <c r="C51" t="n">
         <v>31.20000076293945</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>21.77549362182617</v>
+        <v>21.7755012512207</v>
       </c>
       <c r="C52" t="n">
         <v>32.34999847412109</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>23.7141056060791</v>
+        <v>23.7140941619873</v>
       </c>
       <c r="C53" t="n">
         <v>35.22999954223633</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>22.79191970825195</v>
+        <v>22.79192161560059</v>
       </c>
       <c r="C54" t="n">
         <v>33.86000061035156</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>19.02716064453125</v>
+        <v>19.02715682983398</v>
       </c>
       <c r="C55" t="n">
         <v>28.06999969482422</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>19.32540130615234</v>
+        <v>19.32541275024414</v>
       </c>
       <c r="C56" t="n">
         <v>28.51000022888184</v>
@@ -1609,7 +1609,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>19.01805305480957</v>
+        <v>19.01804733276367</v>
       </c>
       <c r="C57" t="n">
         <v>27.81999969482422</v>
@@ -1634,7 +1634,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>21.65677642822266</v>
+        <v>21.65678024291992</v>
       </c>
       <c r="C58" t="n">
         <v>31.68000030517578</v>
@@ -1659,7 +1659,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>21.12356567382812</v>
+        <v>21.12356376647949</v>
       </c>
       <c r="C59" t="n">
         <v>30.89999961853027</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>20.81191444396973</v>
+        <v>20.81191825866699</v>
       </c>
       <c r="C60" t="n">
         <v>30.20999908447266</v>
@@ -1709,7 +1709,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>24.15312194824219</v>
+        <v>24.15311241149902</v>
       </c>
       <c r="C61" t="n">
         <v>35.06000137329102</v>
@@ -1734,7 +1734,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>25.33114242553711</v>
+        <v>25.33115196228027</v>
       </c>
       <c r="C62" t="n">
         <v>36.77000045776367</v>
@@ -1759,7 +1759,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>25.81339454650879</v>
+        <v>25.81339073181152</v>
       </c>
       <c r="C63" t="n">
         <v>37.47000122070312</v>
@@ -1784,7 +1784,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>25.70523262023926</v>
+        <v>25.70522880554199</v>
       </c>
       <c r="C64" t="n">
         <v>37.06000137329102</v>
@@ -1813,7 +1813,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>25.76765060424805</v>
+        <v>25.76765441894531</v>
       </c>
       <c r="C65" t="n">
         <v>37.15000152587891</v>
@@ -1842,7 +1842,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>25.16421508789062</v>
+        <v>25.16421318054199</v>
       </c>
       <c r="C66" t="n">
         <v>36.27999877929688</v>
@@ -1871,7 +1871,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>25.31142616271973</v>
+        <v>25.31143951416016</v>
       </c>
       <c r="C67" t="n">
         <v>36.22000122070312</v>
@@ -1900,7 +1900,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>24.40994834899902</v>
+        <v>24.40995407104492</v>
       </c>
       <c r="C68" t="n">
         <v>34.93000030517578</v>
@@ -1987,7 +1987,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>25.20329856872559</v>
+        <v>25.20331192016602</v>
       </c>
       <c r="C71" t="n">
         <v>35.79999923706055</v>
@@ -2016,7 +2016,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>27.82734489440918</v>
+        <v>27.82733917236328</v>
       </c>
       <c r="C72" t="n">
         <v>39.22000122070312</v>
@@ -2045,7 +2045,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>29.82818984985352</v>
+        <v>29.82817840576172</v>
       </c>
       <c r="C73" t="n">
         <v>42.04000091552734</v>
@@ -2074,7 +2074,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>31.49555206298828</v>
+        <v>31.49554252624512</v>
       </c>
       <c r="C74" t="n">
         <v>44.38999938964844</v>
@@ -2103,7 +2103,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>33.75183868408203</v>
+        <v>33.7518196105957</v>
       </c>
       <c r="C75" t="n">
         <v>47.56999969482422</v>
@@ -2132,7 +2132,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>35.91570281982422</v>
+        <v>35.91568756103516</v>
       </c>
       <c r="C76" t="n">
         <v>50.31000137329102</v>
@@ -2161,7 +2161,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>36.97225952148438</v>
+        <v>36.97225189208984</v>
       </c>
       <c r="C77" t="n">
         <v>51.79000091552734</v>
@@ -2219,7 +2219,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>38.05210494995117</v>
+        <v>38.0521240234375</v>
       </c>
       <c r="C79" t="n">
         <v>52.9900016784668</v>
@@ -2248,7 +2248,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>37.4704475402832</v>
+        <v>37.47045516967773</v>
       </c>
       <c r="C80" t="n">
         <v>52.18000030517578</v>
@@ -2277,7 +2277,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>40.9617919921875</v>
+        <v>40.96178817749023</v>
       </c>
       <c r="C81" t="n">
         <v>56.75</v>
@@ -2306,7 +2306,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>43.57468414306641</v>
+        <v>43.57467269897461</v>
       </c>
       <c r="C82" t="n">
         <v>60.36999893188477</v>
@@ -2335,7 +2335,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>44.30370330810547</v>
+        <v>44.30369567871094</v>
       </c>
       <c r="C83" t="n">
         <v>61.38000106811523</v>
@@ -2364,7 +2364,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>47.17866134643555</v>
+        <v>47.17867279052734</v>
       </c>
       <c r="C84" t="n">
         <v>65.06999969482422</v>
@@ -2393,7 +2393,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>44.84402084350586</v>
+        <v>44.84402847290039</v>
       </c>
       <c r="C85" t="n">
         <v>61.84999847412109</v>
@@ -2422,7 +2422,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>48.52000427246094</v>
+        <v>48.5200080871582</v>
       </c>
       <c r="C86" t="n">
         <v>66.91999816894531</v>
@@ -2451,7 +2451,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>49.66558456420898</v>
+        <v>49.66556167602539</v>
       </c>
       <c r="C87" t="n">
         <v>68.5</v>
@@ -2480,7 +2480,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>50.87182998657227</v>
+        <v>50.87181091308594</v>
       </c>
       <c r="C88" t="n">
         <v>69.77999877929688</v>
@@ -2509,7 +2509,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>53.47444152832031</v>
+        <v>53.47445678710938</v>
       </c>
       <c r="C89" t="n">
         <v>73.34999847412109</v>
@@ -2538,7 +2538,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>57.34562301635742</v>
+        <v>57.34561538696289</v>
       </c>
       <c r="C90" t="n">
         <v>78.66000366210938</v>
@@ -2567,7 +2567,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>56.75797653198242</v>
+        <v>56.75795745849609</v>
       </c>
       <c r="C91" t="n">
         <v>77.47000122070312</v>
@@ -2596,7 +2596,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>57.90089797973633</v>
+        <v>57.90093231201172</v>
       </c>
       <c r="C92" t="n">
         <v>79.02999877929688</v>
@@ -2625,7 +2625,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>54.57470321655273</v>
+        <v>54.57469940185547</v>
       </c>
       <c r="C93" t="n">
         <v>74.48999786376953</v>
@@ -2654,7 +2654,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>55.86358261108398</v>
+        <v>55.86356735229492</v>
       </c>
       <c r="C94" t="n">
         <v>75.84999847412109</v>
@@ -2683,7 +2683,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>57.36605453491211</v>
+        <v>57.36604309082031</v>
       </c>
       <c r="C95" t="n">
         <v>77.88999938964844</v>
@@ -2712,7 +2712,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>59.41350173950195</v>
+        <v>59.41351318359375</v>
       </c>
       <c r="C96" t="n">
         <v>80.66999816894531</v>
@@ -2741,7 +2741,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>60.94143676757812</v>
+        <v>60.94140243530273</v>
       </c>
       <c r="C97" t="n">
         <v>82.33999633789062</v>
@@ -2770,7 +2770,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>56.87813949584961</v>
+        <v>56.87816619873047</v>
       </c>
       <c r="C98" t="n">
         <v>76.84999847412109</v>
@@ -2799,7 +2799,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>60.71197891235352</v>
+        <v>60.71196746826172</v>
       </c>
       <c r="C99" t="n">
         <v>82.02999877929688</v>
@@ -2828,7 +2828,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>58.90250015258789</v>
+        <v>58.90251922607422</v>
       </c>
       <c r="C100" t="n">
         <v>79.12999725341797</v>
@@ -2857,7 +2857,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>59.18535995483398</v>
+        <v>59.18537139892578</v>
       </c>
       <c r="C101" t="n">
         <v>79.51000213623047</v>
@@ -2886,7 +2886,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>59.7213249206543</v>
+        <v>59.72132110595703</v>
       </c>
       <c r="C102" t="n">
         <v>80.23000335693359</v>
@@ -2915,7 +2915,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>60.61713027954102</v>
+        <v>60.61712646484375</v>
       </c>
       <c r="C103" t="n">
         <v>80.95999908447266</v>
@@ -2944,7 +2944,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>60.53477478027344</v>
+        <v>60.53476333618164</v>
       </c>
       <c r="C104" t="n">
         <v>80.84999847412109</v>
@@ -2973,7 +2973,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>70.00621032714844</v>
+        <v>70.00619506835938</v>
       </c>
       <c r="C105" t="n">
         <v>93.5</v>
@@ -3002,7 +3002,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>69.03544616699219</v>
+        <v>69.03548431396484</v>
       </c>
       <c r="C106" t="n">
         <v>91.73999786376953</v>
@@ -3031,7 +3031,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>73.38497924804688</v>
+        <v>73.385009765625</v>
       </c>
       <c r="C107" t="n">
         <v>97.51999664306641</v>
@@ -3060,7 +3060,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>74.7996826171875</v>
+        <v>74.79971313476562</v>
       </c>
       <c r="C108" t="n">
         <v>99.40000152587891</v>
@@ -3089,7 +3089,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>79.36846160888672</v>
+        <v>79.36845397949219</v>
       </c>
       <c r="C109" t="n">
         <v>104.9700012207031</v>
@@ -3118,7 +3118,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>78.95258331298828</v>
+        <v>78.95257568359375</v>
       </c>
       <c r="C110" t="n">
         <v>104.4199981689453</v>
@@ -3176,7 +3176,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>86.34320831298828</v>
+        <v>86.34323883056641</v>
       </c>
       <c r="C112" t="n">
         <v>113.6100006103516</v>
@@ -3205,7 +3205,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>81.30447387695312</v>
+        <v>81.30445098876953</v>
       </c>
       <c r="C113" t="n">
         <v>106.9800033569336</v>
@@ -3234,7 +3234,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>84.67881774902344</v>
+        <v>84.6788330078125</v>
       </c>
       <c r="C114" t="n">
         <v>111.4199981689453</v>
@@ -3263,7 +3263,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>84.90702819824219</v>
+        <v>84.90704345703125</v>
       </c>
       <c r="C115" t="n">
         <v>111.129997253418</v>
@@ -3292,7 +3292,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>89.41482543945312</v>
+        <v>89.41486358642578</v>
       </c>
       <c r="C116" t="n">
         <v>117.0299987792969</v>
@@ -3321,7 +3321,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>88.97932434082031</v>
+        <v>88.97933197021484</v>
       </c>
       <c r="C117" t="n">
         <v>116.4599990844727</v>
@@ -3350,7 +3350,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>88.68753051757812</v>
+        <v>88.68751525878906</v>
       </c>
       <c r="C118" t="n">
         <v>115.4899978637695</v>
@@ -3379,7 +3379,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>94.94611358642578</v>
+        <v>94.94609832763672</v>
       </c>
       <c r="C119" t="n">
         <v>123.6399993896484</v>
@@ -3408,7 +3408,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>102.8096389770508</v>
+        <v>102.8096313476562</v>
       </c>
       <c r="C120" t="n">
         <v>133.8800048828125</v>
@@ -3437,7 +3437,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>102.0074615478516</v>
+        <v>102.0074844360352</v>
       </c>
       <c r="C121" t="n">
         <v>132.25</v>
@@ -3466,7 +3466,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>97.00156402587891</v>
+        <v>97.00160217285156</v>
       </c>
       <c r="C122" t="n">
         <v>125.7600021362305</v>
@@ -3495,7 +3495,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>95.73661804199219</v>
+        <v>95.73662567138672</v>
       </c>
       <c r="C123" t="n">
         <v>124.120002746582</v>
@@ -3524,7 +3524,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>103.4835586547852</v>
+        <v>103.483512878418</v>
       </c>
       <c r="C124" t="n">
         <v>133.4299926757812</v>
@@ -3553,7 +3553,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>103.8403167724609</v>
+        <v>103.8403244018555</v>
       </c>
       <c r="C125" t="n">
         <v>133.8899993896484</v>
@@ -3582,7 +3582,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>102.9981842041016</v>
+        <v>102.998176574707</v>
       </c>
       <c r="C126" t="n">
         <v>132.1199951171875</v>
@@ -3611,7 +3611,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>99.54463958740234</v>
+        <v>99.54463195800781</v>
       </c>
       <c r="C127" t="n">
         <v>127.6900024414062</v>
@@ -3640,7 +3640,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>107.7691879272461</v>
+        <v>107.7692184448242</v>
       </c>
       <c r="C128" t="n">
         <v>138.2400054931641</v>
@@ -3669,7 +3669,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>105.0935287475586</v>
+        <v>105.0935363769531</v>
       </c>
       <c r="C129" t="n">
         <v>134.1199951171875</v>
@@ -3698,7 +3698,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>100.8308486938477</v>
+        <v>100.8308334350586</v>
       </c>
       <c r="C130" t="n">
         <v>128.6799926757812</v>
@@ -3727,7 +3727,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>95.60439300537109</v>
+        <v>95.60437774658203</v>
       </c>
       <c r="C131" t="n">
         <v>122.0100021362305</v>
@@ -3756,7 +3756,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>101.9334030151367</v>
+        <v>101.9334259033203</v>
       </c>
       <c r="C132" t="n">
         <v>129.3999938964844</v>
@@ -3785,7 +3785,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>105.6200408935547</v>
+        <v>105.6200485229492</v>
       </c>
       <c r="C133" t="n">
         <v>134.0800018310547</v>
@@ -3814,7 +3814,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>108.3771286010742</v>
+        <v>108.3771057128906</v>
       </c>
       <c r="C134" t="n">
         <v>137.5800018310547</v>
@@ -3843,7 +3843,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>114.1512222290039</v>
+        <v>114.1512680053711</v>
       </c>
       <c r="C135" t="n">
         <v>144.9100036621094</v>
@@ -3872,7 +3872,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>116.3676147460938</v>
+        <v>116.3676300048828</v>
       </c>
       <c r="C136" t="n">
         <v>146.8300018310547</v>
@@ -3901,7 +3901,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>123.7143936157227</v>
+        <v>123.7144165039062</v>
       </c>
       <c r="C137" t="n">
         <v>156.1000061035156</v>
@@ -3930,7 +3930,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>122.3648071289062</v>
+        <v>122.3647766113281</v>
       </c>
       <c r="C138" t="n">
         <v>153.5099945068359</v>
@@ -3959,7 +3959,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>122.2770919799805</v>
+        <v>122.2771377563477</v>
       </c>
       <c r="C139" t="n">
         <v>153.3999938964844</v>
@@ -3988,7 +3988,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>119.2480926513672</v>
+        <v>119.2480850219727</v>
       </c>
       <c r="C140" t="n">
         <v>149.6000061035156</v>
@@ -4017,7 +4017,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>120.1697616577148</v>
+        <v>120.1697692871094</v>
       </c>
       <c r="C141" t="n">
         <v>149.8699951171875</v>
@@ -4046,7 +4046,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>131.1467895507812</v>
+        <v>131.1467590332031</v>
       </c>
       <c r="C142" t="n">
         <v>163.5599975585938</v>
@@ -4075,7 +4075,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>132.9268341064453</v>
+        <v>132.9268188476562</v>
       </c>
       <c r="C143" t="n">
         <v>165.7799987792969</v>
@@ -4133,7 +4133,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>152.7400817871094</v>
+        <v>152.7400665283203</v>
       </c>
       <c r="C145" t="n">
         <v>189.5299987792969</v>
@@ -4162,7 +4162,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>161.9030914306641</v>
+        <v>161.9030609130859</v>
       </c>
       <c r="C146" t="n">
         <v>200.8999938964844</v>
@@ -4191,7 +4191,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>146.8893890380859</v>
+        <v>146.8893585205078</v>
       </c>
       <c r="C147" t="n">
         <v>182.2700042724609</v>
@@ -4249,7 +4249,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>149.7776184082031</v>
+        <v>149.777587890625</v>
       </c>
       <c r="C149" t="n">
         <v>184.8000030517578</v>
@@ -4278,7 +4278,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>152.0424346923828</v>
+        <v>152.0424194335938</v>
       </c>
       <c r="C150" t="n">
         <v>186.5500030517578</v>
@@ -4307,7 +4307,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>159.0109405517578</v>
+        <v>159.0108489990234</v>
       </c>
       <c r="C151" t="n">
         <v>195.1000061035156</v>
@@ -4365,7 +4365,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>164.4707946777344</v>
+        <v>164.4707794189453</v>
       </c>
       <c r="C153" t="n">
         <v>200.7700042724609</v>
@@ -4394,7 +4394,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>169.6972961425781</v>
+        <v>169.6972808837891</v>
       </c>
       <c r="C154" t="n">
         <v>207.1499938964844</v>
@@ -4423,7 +4423,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>144.0808868408203</v>
+        <v>144.0809478759766</v>
       </c>
       <c r="C155" t="n">
         <v>175.8800048828125</v>
@@ -4452,7 +4452,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>148.601806640625</v>
+        <v>148.6017456054688</v>
       </c>
       <c r="C156" t="n">
         <v>180.3200073242188</v>
@@ -4481,7 +4481,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>141.5969085693359</v>
+        <v>141.596923828125</v>
       </c>
       <c r="C157" t="n">
         <v>171.8200073242188</v>
@@ -4510,7 +4510,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>151.2471466064453</v>
+        <v>151.2471923828125</v>
       </c>
       <c r="C158" t="n">
         <v>183.5299987792969</v>
@@ -4539,7 +4539,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>152.5739898681641</v>
+        <v>152.5739135742188</v>
       </c>
       <c r="C159" t="n">
         <v>185.1399993896484</v>
@@ -4597,7 +4597,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>169.1192626953125</v>
+        <v>169.1192932128906</v>
       </c>
       <c r="C161" t="n">
         <v>203.6999969482422</v>
@@ -4626,7 +4626,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>157.6204986572266</v>
+        <v>157.6204681396484</v>
       </c>
       <c r="C162" t="n">
         <v>189.8500061035156</v>
@@ -4655,7 +4655,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>173.8755187988281</v>
+        <v>173.8755035400391</v>
       </c>
       <c r="C163" t="n">
         <v>207.9700012207031</v>
@@ -4684,7 +4684,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>178.6577301025391</v>
+        <v>178.6577758789062</v>
       </c>
       <c r="C164" t="n">
         <v>213.6900024414062</v>
@@ -4713,7 +4713,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>190.5465698242188</v>
+        <v>190.5465545654297</v>
       </c>
       <c r="C165" t="n">
         <v>227.9100036621094</v>
@@ -4742,7 +4742,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>195.1673583984375</v>
+        <v>195.1673736572266</v>
       </c>
       <c r="C166" t="n">
         <v>232.0200042724609</v>
@@ -4771,7 +4771,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>197.3207092285156</v>
+        <v>197.3207244873047</v>
       </c>
       <c r="C167" t="n">
         <v>234.5800018310547</v>
@@ -4800,7 +4800,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>185.4855041503906</v>
+        <v>185.4855194091797</v>
       </c>
       <c r="C168" t="n">
         <v>220.5099945068359</v>
@@ -4829,7 +4829,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>184.8686828613281</v>
+        <v>184.8687286376953</v>
       </c>
       <c r="C169" t="n">
         <v>218.3800048828125</v>
@@ -4858,7 +4858,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>193.0971069335938</v>
+        <v>193.0971221923828</v>
       </c>
       <c r="C170" t="n">
         <v>228.1000061035156</v>
@@ -4887,7 +4887,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>184.4115600585938</v>
+        <v>184.4115447998047</v>
       </c>
       <c r="C171" t="n">
         <v>217.8399963378906</v>
@@ -4916,7 +4916,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>159.1160430908203</v>
+        <v>159.1160583496094</v>
       </c>
       <c r="C172" t="n">
         <v>186.7100067138672</v>
@@ -4945,7 +4945,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>187.3412628173828</v>
+        <v>187.3412933349609</v>
       </c>
       <c r="C173" t="n">
         <v>219.8300018310547</v>
@@ -4974,7 +4974,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>211.7570343017578</v>
+        <v>211.7570190429688</v>
       </c>
       <c r="C174" t="n">
         <v>248.4799957275391</v>
@@ -5003,7 +5003,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>214.7618103027344</v>
+        <v>214.7617797851562</v>
       </c>
       <c r="C175" t="n">
         <v>250.5099945068359</v>
@@ -5032,7 +5032,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>227.6041412353516</v>
+        <v>227.6041259765625</v>
       </c>
       <c r="C176" t="n">
         <v>265.489990234375</v>
@@ -5061,7 +5061,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>244.3643035888672</v>
+        <v>244.3642883300781</v>
       </c>
       <c r="C177" t="n">
         <v>285.0400085449219</v>
@@ -5090,7 +5090,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>239.3358001708984</v>
+        <v>239.3358459472656</v>
       </c>
       <c r="C178" t="n">
         <v>277.7099914550781</v>
@@ -5148,7 +5148,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>239.0773010253906</v>
+        <v>239.0772247314453</v>
       </c>
       <c r="C180" t="n">
         <v>277.4100036621094</v>
@@ -5206,7 +5206,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>234.6705322265625</v>
+        <v>234.6706085205078</v>
       </c>
       <c r="C182" t="n">
         <v>270.8200073242188</v>
@@ -5235,7 +5235,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>223.8563385009766</v>
+        <v>223.8563842773438</v>
       </c>
       <c r="C183" t="n">
         <v>258.3399963378906</v>
@@ -5293,7 +5293,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>282.2235412597656</v>
+        <v>282.2235107421875</v>
       </c>
       <c r="C185" t="n">
         <v>323.6700134277344</v>
@@ -5322,7 +5322,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>278.0730895996094</v>
+        <v>278.072998046875</v>
       </c>
       <c r="C186" t="n">
         <v>318.9100036621094</v>
@@ -5351,7 +5351,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>279.5137329101562</v>
+        <v>279.513671875</v>
       </c>
       <c r="C187" t="n">
         <v>318.8900146484375</v>
@@ -5380,7 +5380,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>287.6653442382812</v>
+        <v>287.6653747558594</v>
       </c>
       <c r="C188" t="n">
         <v>328.1900024414062</v>
@@ -5409,7 +5409,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>285.9035034179688</v>
+        <v>285.9034729003906</v>
       </c>
       <c r="C189" t="n">
         <v>326.1799926757812</v>
@@ -5438,7 +5438,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>289.1896057128906</v>
+        <v>289.1895751953125</v>
       </c>
       <c r="C190" t="n">
         <v>328.260009765625</v>
@@ -5467,7 +5467,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>327.4944152832031</v>
+        <v>327.4944763183594</v>
       </c>
       <c r="C191" t="n">
         <v>371.739990234375</v>
@@ -5496,7 +5496,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>352.9282836914062</v>
+        <v>352.92822265625</v>
       </c>
       <c r="C192" t="n">
         <v>400.6099853515625</v>
@@ -5554,7 +5554,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>324.6381530761719</v>
+        <v>324.6381225585938</v>
       </c>
       <c r="C194" t="n">
         <v>366.9800109863281</v>
@@ -5583,7 +5583,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>279.3897399902344</v>
+        <v>279.3897705078125</v>
       </c>
       <c r="C195" t="n">
         <v>315.8299865722656</v>
@@ -5612,7 +5612,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>266.3914794921875</v>
+        <v>266.3914489746094</v>
       </c>
       <c r="C196" t="n">
         <v>299.3299865722656</v>
@@ -5641,7 +5641,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>267.3437194824219</v>
+        <v>267.34375</v>
       </c>
       <c r="C197" t="n">
         <v>300.3999938964844</v>
@@ -5699,7 +5699,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>245.6306610107422</v>
+        <v>245.6306762695312</v>
       </c>
       <c r="C199" t="n">
         <v>274.2699890136719</v>
@@ -5728,7 +5728,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>269.5157775878906</v>
+        <v>269.5156555175781</v>
       </c>
       <c r="C200" t="n">
         <v>300.9400024414062</v>
@@ -5757,7 +5757,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>259.9884643554688</v>
+        <v>259.9884338378906</v>
       </c>
       <c r="C201" t="n">
         <v>288.4200134277344</v>
@@ -5786,7 +5786,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>248.7386779785156</v>
+        <v>248.7387237548828</v>
       </c>
       <c r="C202" t="n">
         <v>275.9400024414062</v>
@@ -5844,7 +5844,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>293.8189086914062</v>
+        <v>293.8188781738281</v>
       </c>
       <c r="C204" t="n">
         <v>323.989990234375</v>
@@ -5873,7 +5873,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>286.4459838867188</v>
+        <v>286.4460144042969</v>
       </c>
       <c r="C205" t="n">
         <v>315.8599853515625</v>
@@ -5902,7 +5902,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>293.982177734375</v>
+        <v>293.9822082519531</v>
       </c>
       <c r="C206" t="n">
         <v>324.1700134277344</v>
@@ -5931,7 +5931,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>268.9251403808594</v>
+        <v>268.9251708984375</v>
       </c>
       <c r="C207" t="n">
         <v>296.5400085449219</v>
@@ -5960,7 +5960,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>269.5755004882812</v>
+        <v>269.5755615234375</v>
       </c>
       <c r="C208" t="n">
         <v>295.1199951171875</v>
@@ -5989,7 +5989,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>274.5263671875</v>
+        <v>274.5263061523438</v>
       </c>
       <c r="C209" t="n">
         <v>300.5400085449219</v>
@@ -6047,7 +6047,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>285.794921875</v>
+        <v>285.7949829101562</v>
       </c>
       <c r="C211" t="n">
         <v>310.6400146484375</v>
@@ -6134,7 +6134,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>279.7684326171875</v>
+        <v>279.7684020996094</v>
       </c>
       <c r="C214" t="n">
         <v>302.1600036621094</v>
@@ -6163,7 +6163,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>263.5929870605469</v>
+        <v>263.593017578125</v>
       </c>
       <c r="C215" t="n">
         <v>284.6900024414062</v>
@@ -6250,7 +6250,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>328.998291015625</v>
+        <v>328.9982299804688</v>
       </c>
       <c r="C218" t="n">
         <v>352.9599914550781</v>
@@ -6279,7 +6279,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>354.7711791992188</v>
+        <v>354.7711486816406</v>
       </c>
       <c r="C219" t="n">
         <v>380.6099853515625</v>
@@ -6308,7 +6308,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>359.6966857910156</v>
+        <v>359.6967163085938</v>
       </c>
       <c r="C220" t="n">
         <v>383.6000061035156</v>
@@ -6337,7 +6337,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>313.3937377929688</v>
+        <v>313.3937683105469</v>
       </c>
       <c r="C221" t="n">
         <v>334.2200012207031</v>
@@ -6366,7 +6366,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>316.1860961914062</v>
+        <v>316.1860656738281</v>
       </c>
       <c r="C222" t="n">
         <v>334.8699951171875</v>
@@ -6395,7 +6395,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>325.0332641601562</v>
+        <v>325.0332946777344</v>
       </c>
       <c r="C223" t="n">
         <v>344.239990234375</v>
@@ -6453,7 +6453,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>350.0530700683594</v>
+        <v>350.0530395507812</v>
       </c>
       <c r="C225" t="n">
         <v>368.5</v>
@@ -6482,7 +6482,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>384.9158630371094</v>
+        <v>384.9158935546875</v>
       </c>
       <c r="C226" t="n">
         <v>405.2000122070312</v>
@@ -6511,7 +6511,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>374.0390625</v>
+        <v>374.0390319824219</v>
       </c>
       <c r="C227" t="n">
         <v>393.75</v>
@@ -6569,7 +6569,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>371.4631652832031</v>
+        <v>371.4631958007812</v>
       </c>
       <c r="C229" t="n">
         <v>388.989990234375</v>
@@ -6598,7 +6598,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>393.4173889160156</v>
+        <v>393.4173583984375</v>
       </c>
       <c r="C230" t="n">
         <v>411.9800109863281</v>
@@ -6627,7 +6627,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>378.7303466796875</v>
+        <v>378.7303161621094</v>
       </c>
       <c r="C231" t="n">
         <v>396.6000061035156</v>
@@ -6714,7 +6714,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>353.9278564453125</v>
+        <v>353.9277954101562</v>
       </c>
       <c r="C234" t="n">
         <v>368.2900085449219</v>
@@ -6743,7 +6743,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>354.5317993164062</v>
+        <v>354.5317687988281</v>
       </c>
       <c r="C235" t="n">
         <v>366.6400146484375</v>
@@ -6772,7 +6772,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>355.3730773925781</v>
+        <v>355.373046875</v>
       </c>
       <c r="C236" t="n">
         <v>367.510009765625</v>
@@ -6830,7 +6830,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>394.0315246582031</v>
+        <v>394.031494140625</v>
       </c>
       <c r="C238" t="n">
         <v>405.1900024414062</v>
@@ -6888,7 +6888,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>347.0908203125</v>
+        <v>347.0908508300781</v>
       </c>
       <c r="C240" t="n">
         <v>356.9200134277344</v>
@@ -6917,7 +6917,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>336.7881164550781</v>
+        <v>336.7881469726562</v>
       </c>
       <c r="C241" t="n">
         <v>344.1000061035156</v>
@@ -6975,7 +6975,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>372.6299743652344</v>
+        <v>372.6300048828125</v>
       </c>
       <c r="C243" t="n">
         <v>380.7200012207031</v>
